--- a/Data/EXCEL/Transfer/salemon/202206/6785-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6785-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAA12E37-59D0-427D-A3C1-1FB497834D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8087EF9A-7CFC-42D4-87A7-9FA21502F04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6785-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -1218,21 +1218,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="12.125" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="10" width="10.5" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="10.5" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="15" width="10.5" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="11.75" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="5" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="13.875" customWidth="1"/>
+    <col min="8" max="8" width="12.625" customWidth="1"/>
+    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="12.625" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="12.625" customWidth="1"/>
+    <col min="14" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="12.625" customWidth="1"/>
+    <col min="17" max="17" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1385,25 +1385,25 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>45.3</v>
+        <v>47</v>
       </c>
       <c r="C5" s="7">
-        <v>47</v>
+        <v>53.6</v>
       </c>
       <c r="D5" s="7">
-        <v>48.2</v>
+        <v>54.2</v>
       </c>
       <c r="E5" s="7">
-        <v>43.9</v>
+        <v>44.05</v>
       </c>
       <c r="F5" s="8">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="G5" s="8">
-        <v>3.75</v>
+        <v>14.04</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
@@ -1438,25 +1438,25 @@
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>50.1</v>
+        <v>45.3</v>
       </c>
       <c r="C6" s="7">
-        <v>45.3</v>
+        <v>47</v>
       </c>
       <c r="D6" s="7">
-        <v>50.2</v>
+        <v>48.2</v>
       </c>
       <c r="E6" s="7">
-        <v>44.9</v>
-      </c>
-      <c r="F6" s="10">
-        <v>-4.8</v>
-      </c>
-      <c r="G6" s="10">
-        <v>-9.58</v>
+        <v>43.9</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="G6" s="8">
+        <v>3.75</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -1491,25 +1491,25 @@
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>52.2</v>
+        <v>50.1</v>
       </c>
       <c r="C7" s="7">
-        <v>50.1</v>
+        <v>45.3</v>
       </c>
       <c r="D7" s="7">
-        <v>55.3</v>
+        <v>50.2</v>
       </c>
       <c r="E7" s="7">
-        <v>47.85</v>
+        <v>44.9</v>
       </c>
       <c r="F7" s="10">
-        <v>-2.1</v>
+        <v>-4.8</v>
       </c>
       <c r="G7" s="10">
-        <v>-4.0199999999999996</v>
+        <v>-9.58</v>
       </c>
       <c r="H7" s="9">
         <v>0</v>
@@ -1544,25 +1544,25 @@
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>44.4</v>
+        <v>52.2</v>
       </c>
       <c r="C8" s="7">
-        <v>52.2</v>
+        <v>50.1</v>
       </c>
       <c r="D8" s="7">
-        <v>55.2</v>
+        <v>55.3</v>
       </c>
       <c r="E8" s="7">
-        <v>45</v>
-      </c>
-      <c r="F8" s="8">
-        <v>7.8</v>
-      </c>
-      <c r="G8" s="8">
-        <v>17.57</v>
+        <v>47.85</v>
+      </c>
+      <c r="F8" s="10">
+        <v>-2.1</v>
+      </c>
+      <c r="G8" s="10">
+        <v>-4.0199999999999996</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -1597,25 +1597,25 @@
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>45.75</v>
+        <v>44.4</v>
       </c>
       <c r="C9" s="7">
-        <v>44.4</v>
+        <v>52.2</v>
       </c>
       <c r="D9" s="7">
-        <v>46.25</v>
+        <v>55.2</v>
       </c>
       <c r="E9" s="7">
-        <v>42.8</v>
-      </c>
-      <c r="F9" s="10">
-        <v>-1.35</v>
-      </c>
-      <c r="G9" s="10">
-        <v>-2.95</v>
+        <v>45</v>
+      </c>
+      <c r="F9" s="8">
+        <v>7.8</v>
+      </c>
+      <c r="G9" s="8">
+        <v>17.57</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
@@ -1650,25 +1650,25 @@
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>49.15</v>
+        <v>45.75</v>
       </c>
       <c r="C10" s="7">
-        <v>45.75</v>
+        <v>44.4</v>
       </c>
       <c r="D10" s="7">
-        <v>49.15</v>
+        <v>46.25</v>
       </c>
       <c r="E10" s="7">
-        <v>45.35</v>
+        <v>42.8</v>
       </c>
       <c r="F10" s="10">
-        <v>-3.4</v>
+        <v>-1.35</v>
       </c>
       <c r="G10" s="10">
-        <v>-6.92</v>
+        <v>-2.95</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -1682,8 +1682,8 @@
       <c r="K10" s="9">
         <v>0</v>
       </c>
-      <c r="L10" s="10">
-        <v>-100</v>
+      <c r="L10" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M10" s="9">
         <v>0</v>
@@ -1697,31 +1697,31 @@
       <c r="P10" s="9">
         <v>0</v>
       </c>
-      <c r="Q10" s="10">
-        <v>-100</v>
+      <c r="Q10" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>51.6</v>
+        <v>49.15</v>
       </c>
       <c r="C11" s="7">
+        <v>45.75</v>
+      </c>
+      <c r="D11" s="7">
         <v>49.15</v>
       </c>
-      <c r="D11" s="7">
-        <v>54.9</v>
-      </c>
       <c r="E11" s="7">
-        <v>45.6</v>
+        <v>45.35</v>
       </c>
       <c r="F11" s="10">
-        <v>-2.4500000000000002</v>
+        <v>-3.4</v>
       </c>
       <c r="G11" s="10">
-        <v>-4.75</v>
+        <v>-6.92</v>
       </c>
       <c r="H11" s="9">
         <v>0</v>
@@ -1756,25 +1756,25 @@
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>52.7</v>
+        <v>51.6</v>
       </c>
       <c r="C12" s="7">
-        <v>51.6</v>
+        <v>49.15</v>
       </c>
       <c r="D12" s="7">
-        <v>53.5</v>
+        <v>54.9</v>
       </c>
       <c r="E12" s="7">
-        <v>49.25</v>
+        <v>45.6</v>
       </c>
       <c r="F12" s="10">
-        <v>-1.1000000000000001</v>
+        <v>-2.4500000000000002</v>
       </c>
       <c r="G12" s="10">
-        <v>-2.09</v>
+        <v>-4.75</v>
       </c>
       <c r="H12" s="9">
         <v>0</v>
@@ -1782,8 +1782,8 @@
       <c r="I12" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="10">
-        <v>-100</v>
+      <c r="J12" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K12" s="9">
         <v>0</v>
@@ -1797,8 +1797,8 @@
       <c r="N12" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O12" s="10">
-        <v>-100</v>
+      <c r="O12" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P12" s="9">
         <v>0</v>
@@ -1809,25 +1809,25 @@
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>49.9</v>
+        <v>52.7</v>
       </c>
       <c r="C13" s="7">
-        <v>52.7</v>
+        <v>51.6</v>
       </c>
       <c r="D13" s="7">
-        <v>54.5</v>
+        <v>53.5</v>
       </c>
       <c r="E13" s="7">
-        <v>49.55</v>
-      </c>
-      <c r="F13" s="8">
-        <v>2.8</v>
-      </c>
-      <c r="G13" s="8">
-        <v>5.61</v>
+        <v>49.25</v>
+      </c>
+      <c r="F13" s="10">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="G13" s="10">
+        <v>-2.09</v>
       </c>
       <c r="H13" s="9">
         <v>0</v>
@@ -1835,14 +1835,14 @@
       <c r="I13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J13" s="9" t="s">
-        <v>17</v>
+      <c r="J13" s="10">
+        <v>-100</v>
       </c>
       <c r="K13" s="9">
         <v>0</v>
       </c>
-      <c r="L13" s="9" t="s">
-        <v>17</v>
+      <c r="L13" s="10">
+        <v>-100</v>
       </c>
       <c r="M13" s="9">
         <v>0</v>
@@ -1850,37 +1850,37 @@
       <c r="N13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O13" s="9" t="s">
-        <v>17</v>
+      <c r="O13" s="10">
+        <v>-100</v>
       </c>
       <c r="P13" s="9">
         <v>0</v>
       </c>
-      <c r="Q13" s="9" t="s">
-        <v>17</v>
+      <c r="Q13" s="10">
+        <v>-100</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="C14" s="7">
-        <v>49.9</v>
+        <v>52.7</v>
       </c>
       <c r="D14" s="7">
-        <v>50.1</v>
+        <v>54.5</v>
       </c>
       <c r="E14" s="7">
-        <v>47.85</v>
-      </c>
-      <c r="F14" s="10">
-        <v>-0.1</v>
-      </c>
-      <c r="G14" s="10">
-        <v>-0.2</v>
+        <v>49.55</v>
+      </c>
+      <c r="F14" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="G14" s="8">
+        <v>5.61</v>
       </c>
       <c r="H14" s="9">
         <v>0</v>
@@ -1915,25 +1915,25 @@
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="C15" s="7">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="D15" s="7">
-        <v>51.2</v>
+        <v>50.1</v>
       </c>
       <c r="E15" s="7">
         <v>47.85</v>
       </c>
-      <c r="F15" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="G15" s="8">
-        <v>1.01</v>
+      <c r="F15" s="10">
+        <v>-0.1</v>
+      </c>
+      <c r="G15" s="10">
+        <v>-0.2</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -1968,25 +1968,25 @@
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7">
-        <v>51.5</v>
+        <v>49.5</v>
       </c>
       <c r="C16" s="7">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="D16" s="7">
-        <v>52.1</v>
+        <v>51.2</v>
       </c>
       <c r="E16" s="7">
-        <v>49</v>
-      </c>
-      <c r="F16" s="10">
-        <v>-2</v>
-      </c>
-      <c r="G16" s="10">
-        <v>-3.88</v>
+        <v>47.85</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G16" s="8">
+        <v>1.01</v>
       </c>
       <c r="H16" s="9">
         <v>0</v>
@@ -2021,25 +2021,25 @@
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7">
         <v>51.5</v>
       </c>
       <c r="C17" s="7">
-        <v>51.5</v>
+        <v>49.5</v>
       </c>
       <c r="D17" s="7">
-        <v>53.1</v>
+        <v>52.1</v>
       </c>
       <c r="E17" s="7">
-        <v>47.5</v>
-      </c>
-      <c r="F17" s="9">
-        <v>0</v>
-      </c>
-      <c r="G17" s="9">
-        <v>0</v>
+        <v>49</v>
+      </c>
+      <c r="F17" s="10">
+        <v>-2</v>
+      </c>
+      <c r="G17" s="10">
+        <v>-3.88</v>
       </c>
       <c r="H17" s="9">
         <v>0</v>
@@ -2074,25 +2074,25 @@
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7">
-        <v>49.4</v>
+        <v>51.5</v>
       </c>
       <c r="C18" s="7">
         <v>51.5</v>
       </c>
       <c r="D18" s="7">
-        <v>55.1</v>
+        <v>53.1</v>
       </c>
       <c r="E18" s="7">
-        <v>48.5</v>
-      </c>
-      <c r="F18" s="8">
-        <v>2.1</v>
-      </c>
-      <c r="G18" s="8">
-        <v>4.25</v>
+        <v>47.5</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
       </c>
       <c r="H18" s="9">
         <v>0</v>
@@ -2127,25 +2127,25 @@
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7">
-        <v>49.75</v>
+        <v>49.4</v>
       </c>
       <c r="C19" s="7">
-        <v>49.4</v>
+        <v>51.5</v>
       </c>
       <c r="D19" s="7">
-        <v>52.1</v>
+        <v>55.1</v>
       </c>
       <c r="E19" s="7">
         <v>48.5</v>
       </c>
-      <c r="F19" s="10">
-        <v>-0.35</v>
-      </c>
-      <c r="G19" s="10">
-        <v>-0.7</v>
+      <c r="F19" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="G19" s="8">
+        <v>4.25</v>
       </c>
       <c r="H19" s="9">
         <v>0</v>
@@ -2180,25 +2180,25 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7">
+        <v>49.75</v>
+      </c>
+      <c r="C20" s="7">
+        <v>49.4</v>
+      </c>
+      <c r="D20" s="7">
+        <v>52.1</v>
+      </c>
+      <c r="E20" s="7">
         <v>48.5</v>
       </c>
-      <c r="C20" s="7">
-        <v>49.75</v>
-      </c>
-      <c r="D20" s="7">
-        <v>52.3</v>
-      </c>
-      <c r="E20" s="7">
-        <v>48.05</v>
-      </c>
-      <c r="F20" s="8">
-        <v>1.25</v>
-      </c>
-      <c r="G20" s="8">
-        <v>2.58</v>
+      <c r="F20" s="10">
+        <v>-0.35</v>
+      </c>
+      <c r="G20" s="10">
+        <v>-0.7</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
@@ -2233,25 +2233,25 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7">
-        <v>49</v>
+        <v>48.5</v>
       </c>
       <c r="C21" s="7">
-        <v>48.5</v>
+        <v>49.75</v>
       </c>
       <c r="D21" s="7">
-        <v>53.5</v>
+        <v>52.3</v>
       </c>
       <c r="E21" s="7">
-        <v>48</v>
-      </c>
-      <c r="F21" s="10">
-        <v>-0.5</v>
-      </c>
-      <c r="G21" s="10">
-        <v>-1.02</v>
+        <v>48.05</v>
+      </c>
+      <c r="F21" s="8">
+        <v>1.25</v>
+      </c>
+      <c r="G21" s="8">
+        <v>2.58</v>
       </c>
       <c r="H21" s="9">
         <v>0</v>
@@ -2286,25 +2286,25 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7">
-        <v>44.05</v>
+        <v>49</v>
       </c>
       <c r="C22" s="7">
-        <v>49</v>
+        <v>48.5</v>
       </c>
       <c r="D22" s="7">
-        <v>53.1</v>
+        <v>53.5</v>
       </c>
       <c r="E22" s="7">
-        <v>44.05</v>
-      </c>
-      <c r="F22" s="8">
-        <v>4.95</v>
-      </c>
-      <c r="G22" s="8">
-        <v>11.24</v>
+        <v>48</v>
+      </c>
+      <c r="F22" s="10">
+        <v>-0.5</v>
+      </c>
+      <c r="G22" s="10">
+        <v>-1.02</v>
       </c>
       <c r="H22" s="9">
         <v>0</v>
@@ -2316,7 +2316,7 @@
         <v>17</v>
       </c>
       <c r="K22" s="9">
-        <v>6.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>17</v>
@@ -2331,7 +2331,7 @@
         <v>17</v>
       </c>
       <c r="P22" s="9">
-        <v>6.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="9" t="s">
         <v>17</v>
@@ -2339,31 +2339,31 @@
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7">
-        <v>49.3</v>
+        <v>44.05</v>
       </c>
       <c r="C23" s="7">
+        <v>49</v>
+      </c>
+      <c r="D23" s="7">
+        <v>53.1</v>
+      </c>
+      <c r="E23" s="7">
         <v>44.05</v>
       </c>
-      <c r="D23" s="7">
-        <v>51.9</v>
-      </c>
-      <c r="E23" s="7">
-        <v>43.55</v>
-      </c>
-      <c r="F23" s="10">
-        <v>-5.25</v>
-      </c>
-      <c r="G23" s="10">
-        <v>-10.65</v>
+      <c r="F23" s="8">
+        <v>4.95</v>
+      </c>
+      <c r="G23" s="8">
+        <v>11.24</v>
       </c>
       <c r="H23" s="9">
         <v>0</v>
       </c>
-      <c r="I23" s="10">
-        <v>-100</v>
+      <c r="I23" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>17</v>
@@ -2377,8 +2377,8 @@
       <c r="M23" s="9">
         <v>0</v>
       </c>
-      <c r="N23" s="10">
-        <v>-100</v>
+      <c r="N23" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>17</v>
@@ -2392,31 +2392,31 @@
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7">
-        <v>45</v>
+        <v>49.3</v>
       </c>
       <c r="C24" s="7">
-        <v>49.3</v>
+        <v>44.05</v>
       </c>
       <c r="D24" s="7">
-        <v>73.599999999999994</v>
+        <v>51.9</v>
       </c>
       <c r="E24" s="7">
-        <v>43.1</v>
-      </c>
-      <c r="F24" s="8">
-        <v>4.3</v>
-      </c>
-      <c r="G24" s="8">
-        <v>9.56</v>
+        <v>43.55</v>
+      </c>
+      <c r="F24" s="10">
+        <v>-5.25</v>
+      </c>
+      <c r="G24" s="10">
+        <v>-10.65</v>
       </c>
       <c r="H24" s="9">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I24" s="10">
+        <v>-100</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>17</v>
@@ -2428,10 +2428,10 @@
         <v>17</v>
       </c>
       <c r="M24" s="9">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N24" s="10">
+        <v>-100</v>
       </c>
       <c r="O24" s="9" t="s">
         <v>17</v>
@@ -2445,28 +2445,28 @@
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>17</v>
+        <v>44105</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45</v>
+      </c>
+      <c r="C25" s="7">
+        <v>49.3</v>
+      </c>
+      <c r="D25" s="7">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="E25" s="7">
+        <v>43.1</v>
+      </c>
+      <c r="F25" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G25" s="8">
+        <v>9.56</v>
       </c>
       <c r="H25" s="9">
-        <v>0</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="I25" s="9" t="s">
         <v>17</v>
@@ -2475,13 +2475,13 @@
         <v>17</v>
       </c>
       <c r="K25" s="9">
-        <v>0</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="L25" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M25" s="9">
-        <v>0</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="N25" s="9" t="s">
         <v>17</v>
@@ -2490,7 +2490,7 @@
         <v>17</v>
       </c>
       <c r="P25" s="9">
-        <v>0</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q25" s="9" t="s">
         <v>17</v>
@@ -2498,7 +2498,7 @@
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>17</v>
@@ -2551,7 +2551,7 @@
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>17</v>
@@ -2604,54 +2604,107 @@
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
+        <v>44013</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="9">
+        <v>0</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" s="9">
+        <v>0</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M28" s="9">
+        <v>0</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
         <v>43983</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H28" s="9">
-        <v>0</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K28" s="9">
-        <v>0</v>
-      </c>
-      <c r="L28" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M28" s="9">
-        <v>0</v>
-      </c>
-      <c r="N28" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O28" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P28" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="9" t="s">
+      <c r="B29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" s="9">
+        <v>0</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29" s="9">
+        <v>0</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M29" s="9">
+        <v>0</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P29" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="9" t="s">
         <v>17</v>
       </c>
     </row>
